--- a/DB2/results/without_time2vec/Trans_rslt.xlsx
+++ b/DB2/results/without_time2vec/Trans_rslt.xlsx
@@ -198,8 +198,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,28 +511,28 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1574,6 +1577,10 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D44">
+        <f>AVERAGE(D2:D41)</f>
+        <v>0.86358415335416794</v>
+      </c>
       <c r="F44">
         <f>AVERAGE(F2:F41)</f>
         <v>0.75903707146644595</v>
